--- a/docs/CodeSystem-regulatory-compliance-cs.xlsx
+++ b/docs/CodeSystem-regulatory-compliance-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-regulatory-compliance-cs.xlsx
+++ b/docs/CodeSystem-regulatory-compliance-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-regulatory-compliance-cs.xlsx
+++ b/docs/CodeSystem-regulatory-compliance-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-regulatory-compliance-cs.xlsx
+++ b/docs/CodeSystem-regulatory-compliance-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-regulatory-compliance-cs.xlsx
+++ b/docs/CodeSystem-regulatory-compliance-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="120">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/CodeSystem/regulatory-compliance-cs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/regulatory-compliance-cs</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,13 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,12 +93,12 @@
     <t>Copyright</t>
   </si>
   <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
+  </si>
+  <si>
     <t>Case Sensitive</t>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>Value Set (all codes)</t>
   </si>
   <si>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>21</t>
+    <t>26</t>
   </si>
   <si>
     <t>Level</t>
@@ -328,6 +328,51 @@
   </si>
   <si>
     <t>Diving instructor certification</t>
+  </si>
+  <si>
+    <t>compliance-status</t>
+  </si>
+  <si>
+    <t>Compliance Status</t>
+  </si>
+  <si>
+    <t>Overall compliance status against the assessed regulatory standard</t>
+  </si>
+  <si>
+    <t>standards-version</t>
+  </si>
+  <si>
+    <t>Standards Version</t>
+  </si>
+  <si>
+    <t>Version or edition of the regulatory standard assessed against</t>
+  </si>
+  <si>
+    <t>certification-level</t>
+  </si>
+  <si>
+    <t>Certification Level</t>
+  </si>
+  <si>
+    <t>Certification level held by the individual under the standard</t>
+  </si>
+  <si>
+    <t>expiration-date</t>
+  </si>
+  <si>
+    <t>Certification Expiration Date</t>
+  </si>
+  <si>
+    <t>Date on which the certification or compliance status expires</t>
+  </si>
+  <si>
+    <t>restrictions-limitations</t>
+  </si>
+  <si>
+    <t>Restrictions and Limitations</t>
+  </si>
+  <si>
+    <t>Restrictions or limitations attached to the certification or compliance status</t>
   </si>
 </sst>
 </file>
@@ -574,14 +619,16 @@
       <c r="A14" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -637,7 +684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -948,6 +995,76 @@
         <v>104</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
